--- a/docs/tech/ezMemo/ezEKP Java ezMemo 테이블 정의서.xlsx
+++ b/docs/tech/ezMemo/ezEKP Java ezMemo 테이블 정의서.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NC388\Desktop\메모 최종\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NC388\Desktop\ezMemo\2차 문서\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12285" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="15210" windowHeight="10080" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="ERD" sheetId="3" r:id="rId1"/>
@@ -523,7 +523,7 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>default 1 / 0: 닫힘 1: 조회중</t>
+    <t>default 0 / 0: 닫힘 1: 조회중</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
